--- a/Mantenimiento/excels/LIMA-LIMA-VILLA_EL_SALVADOR.xlsx
+++ b/Mantenimiento/excels/LIMA-LIMA-VILLA_EL_SALVADOR.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L46"/>
+  <dimension ref="A1:K46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -484,11 +484,6 @@
           <t>siniestros</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>mantenimiento</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -508,7 +503,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VILLA_EL_SALVADOR</t>
+          <t>VILLA EL SALVADOR</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -536,11 +531,6 @@
       <c r="K2" t="n">
         <v>0</v>
       </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -560,7 +550,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VILLA_EL_SALVADOR</t>
+          <t>VILLA EL SALVADOR</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -588,11 +578,6 @@
       <c r="K3" t="n">
         <v>0</v>
       </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -612,7 +597,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VILLA_EL_SALVADOR</t>
+          <t>VILLA EL SALVADOR</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -640,11 +625,6 @@
       <c r="K4" t="n">
         <v>0</v>
       </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -664,7 +644,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VILLA_EL_SALVADOR</t>
+          <t>VILLA EL SALVADOR</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -692,11 +672,6 @@
       <c r="K5" t="n">
         <v>0</v>
       </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -716,7 +691,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VILLA_EL_SALVADOR</t>
+          <t>VILLA EL SALVADOR</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -744,11 +719,6 @@
       <c r="K6" t="n">
         <v>0</v>
       </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -768,7 +738,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VILLA_EL_SALVADOR</t>
+          <t>VILLA EL SALVADOR</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -796,11 +766,6 @@
       <c r="K7" t="n">
         <v>0</v>
       </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -820,7 +785,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VILLA_EL_SALVADOR</t>
+          <t>VILLA EL SALVADOR</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -848,11 +813,6 @@
       <c r="K8" t="n">
         <v>0</v>
       </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -872,7 +832,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VILLA_EL_SALVADOR</t>
+          <t>VILLA EL SALVADOR</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -900,11 +860,6 @@
       <c r="K9" t="n">
         <v>0</v>
       </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -924,7 +879,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VILLA_EL_SALVADOR</t>
+          <t>VILLA EL SALVADOR</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -952,11 +907,6 @@
       <c r="K10" t="n">
         <v>0</v>
       </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -976,7 +926,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VILLA_EL_SALVADOR</t>
+          <t>VILLA EL SALVADOR</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1004,11 +954,6 @@
       <c r="K11" t="n">
         <v>0</v>
       </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1028,7 +973,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VILLA_EL_SALVADOR</t>
+          <t>VILLA EL SALVADOR</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1056,11 +1001,6 @@
       <c r="K12" t="n">
         <v>0</v>
       </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1080,7 +1020,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VILLA_EL_SALVADOR</t>
+          <t>VILLA EL SALVADOR</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1108,11 +1048,6 @@
       <c r="K13" t="n">
         <v>0</v>
       </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1132,7 +1067,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VILLA_EL_SALVADOR</t>
+          <t>VILLA EL SALVADOR</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1160,11 +1095,6 @@
       <c r="K14" t="n">
         <v>0</v>
       </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1184,7 +1114,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VILLA_EL_SALVADOR</t>
+          <t>VILLA EL SALVADOR</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1212,11 +1142,6 @@
       <c r="K15" t="n">
         <v>0</v>
       </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1236,7 +1161,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VILLA_EL_SALVADOR</t>
+          <t>VILLA EL SALVADOR</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1264,11 +1189,6 @@
       <c r="K16" t="n">
         <v>0</v>
       </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1288,7 +1208,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VILLA_EL_SALVADOR</t>
+          <t>VILLA EL SALVADOR</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1316,11 +1236,6 @@
       <c r="K17" t="n">
         <v>0</v>
       </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1340,7 +1255,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VILLA_EL_SALVADOR</t>
+          <t>VILLA EL SALVADOR</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1368,11 +1283,6 @@
       <c r="K18" t="n">
         <v>0</v>
       </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1392,7 +1302,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VILLA_EL_SALVADOR</t>
+          <t>VILLA EL SALVADOR</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1420,11 +1330,6 @@
       <c r="K19" t="n">
         <v>1</v>
       </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1444,7 +1349,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VILLA_EL_SALVADOR</t>
+          <t>VILLA EL SALVADOR</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1472,11 +1377,6 @@
       <c r="K20" t="n">
         <v>0</v>
       </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1496,7 +1396,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VILLA_EL_SALVADOR</t>
+          <t>VILLA EL SALVADOR</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1524,11 +1424,6 @@
       <c r="K21" t="n">
         <v>0</v>
       </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1548,7 +1443,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VILLA_EL_SALVADOR</t>
+          <t>VILLA EL SALVADOR</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1576,11 +1471,6 @@
       <c r="K22" t="n">
         <v>0</v>
       </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1600,7 +1490,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VILLA_EL_SALVADOR</t>
+          <t>VILLA EL SALVADOR</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1628,11 +1518,6 @@
       <c r="K23" t="n">
         <v>0</v>
       </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1652,7 +1537,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VILLA_EL_SALVADOR</t>
+          <t>VILLA EL SALVADOR</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1680,11 +1565,6 @@
       <c r="K24" t="n">
         <v>0</v>
       </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1704,7 +1584,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VILLA_EL_SALVADOR</t>
+          <t>VILLA EL SALVADOR</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1732,11 +1612,6 @@
       <c r="K25" t="n">
         <v>0</v>
       </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1756,7 +1631,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VILLA_EL_SALVADOR</t>
+          <t>VILLA EL SALVADOR</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1784,11 +1659,6 @@
       <c r="K26" t="n">
         <v>0</v>
       </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1808,7 +1678,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VILLA_EL_SALVADOR</t>
+          <t>VILLA EL SALVADOR</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1836,11 +1706,6 @@
       <c r="K27" t="n">
         <v>0</v>
       </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1860,7 +1725,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VILLA_EL_SALVADOR</t>
+          <t>VILLA EL SALVADOR</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1888,11 +1753,6 @@
       <c r="K28" t="n">
         <v>0</v>
       </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1912,7 +1772,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VILLA_EL_SALVADOR</t>
+          <t>VILLA EL SALVADOR</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1940,11 +1800,6 @@
       <c r="K29" t="n">
         <v>0</v>
       </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1964,7 +1819,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VILLA_EL_SALVADOR</t>
+          <t>VILLA EL SALVADOR</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1992,11 +1847,6 @@
       <c r="K30" t="n">
         <v>0</v>
       </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2016,7 +1866,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VILLA_EL_SALVADOR</t>
+          <t>VILLA EL SALVADOR</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2044,11 +1894,6 @@
       <c r="K31" t="n">
         <v>0</v>
       </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2068,7 +1913,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VILLA_EL_SALVADOR</t>
+          <t>VILLA EL SALVADOR</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2096,11 +1941,6 @@
       <c r="K32" t="n">
         <v>0</v>
       </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2120,7 +1960,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VILLA_EL_SALVADOR</t>
+          <t>VILLA EL SALVADOR</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2148,11 +1988,6 @@
       <c r="K33" t="n">
         <v>0</v>
       </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2172,7 +2007,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VILLA_EL_SALVADOR</t>
+          <t>VILLA EL SALVADOR</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2200,11 +2035,6 @@
       <c r="K34" t="n">
         <v>0</v>
       </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2224,7 +2054,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VILLA_EL_SALVADOR</t>
+          <t>VILLA EL SALVADOR</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2252,11 +2082,6 @@
       <c r="K35" t="n">
         <v>0</v>
       </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2276,7 +2101,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VILLA_EL_SALVADOR</t>
+          <t>VILLA EL SALVADOR</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2304,11 +2129,6 @@
       <c r="K36" t="n">
         <v>0</v>
       </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2328,7 +2148,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VILLA_EL_SALVADOR</t>
+          <t>VILLA EL SALVADOR</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2356,11 +2176,6 @@
       <c r="K37" t="n">
         <v>0</v>
       </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2380,7 +2195,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VILLA_EL_SALVADOR</t>
+          <t>VILLA EL SALVADOR</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2408,11 +2223,6 @@
       <c r="K38" t="n">
         <v>0</v>
       </c>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2432,7 +2242,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VILLA_EL_SALVADOR</t>
+          <t>VILLA EL SALVADOR</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2460,11 +2270,6 @@
       <c r="K39" t="n">
         <v>0</v>
       </c>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2484,7 +2289,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VILLA_EL_SALVADOR</t>
+          <t>VILLA EL SALVADOR</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2512,11 +2317,6 @@
       <c r="K40" t="n">
         <v>0</v>
       </c>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2536,7 +2336,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VILLA_EL_SALVADOR</t>
+          <t>VILLA EL SALVADOR</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2564,11 +2364,6 @@
       <c r="K41" t="n">
         <v>0</v>
       </c>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2588,7 +2383,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VILLA_EL_SALVADOR</t>
+          <t>VILLA EL SALVADOR</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2616,11 +2411,6 @@
       <c r="K42" t="n">
         <v>0</v>
       </c>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2640,7 +2430,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VILLA_EL_SALVADOR</t>
+          <t>VILLA EL SALVADOR</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -2668,11 +2458,6 @@
       <c r="K43" t="n">
         <v>0</v>
       </c>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2692,7 +2477,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VILLA_EL_SALVADOR</t>
+          <t>VILLA EL SALVADOR</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2720,11 +2505,6 @@
       <c r="K44" t="n">
         <v>0</v>
       </c>
-      <c r="L44" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2744,7 +2524,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VILLA_EL_SALVADOR</t>
+          <t>VILLA EL SALVADOR</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2772,11 +2552,6 @@
       <c r="K45" t="n">
         <v>0</v>
       </c>
-      <c r="L45" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2796,7 +2571,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VILLA_EL_SALVADOR</t>
+          <t>VILLA EL SALVADOR</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2823,11 +2598,6 @@
       </c>
       <c r="K46" t="n">
         <v>0</v>
-      </c>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
       </c>
     </row>
   </sheetData>

--- a/Mantenimiento/excels/LIMA-LIMA-VILLA_EL_SALVADOR.xlsx
+++ b/Mantenimiento/excels/LIMA-LIMA-VILLA_EL_SALVADOR.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,61 +413,61 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K46"/>
+  <dimension ref="A1:K45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ubigeo_gestor</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>departamento</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>provincia</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>distrito</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>codigo_ce</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>descripcion</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>longitud</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>alumnos</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>docentes</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>siniestros</t>
         </is>
@@ -516,20 +504,30 @@
           <t>MONTESSORI DE VILLA</t>
         </is>
       </c>
-      <c r="G2" t="n">
-        <v>-12.2184</v>
-      </c>
-      <c r="H2" t="n">
-        <v>-76.93516</v>
-      </c>
-      <c r="I2" t="n">
-        <v>214</v>
-      </c>
-      <c r="J2" t="n">
-        <v>15</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>-12.2184</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>-76.93516</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>214</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -563,20 +561,30 @@
           <t>557</t>
         </is>
       </c>
-      <c r="G3" t="n">
-        <v>-12.2286</v>
-      </c>
-      <c r="H3" t="n">
-        <v>-76.92331</v>
-      </c>
-      <c r="I3" t="n">
-        <v>392</v>
-      </c>
-      <c r="J3" t="n">
-        <v>15</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>-12.2286</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>-76.92331</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>392</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -610,20 +618,30 @@
           <t>558 CASA MONTESSORI</t>
         </is>
       </c>
-      <c r="G4" t="n">
-        <v>-12.2322</v>
-      </c>
-      <c r="H4" t="n">
-        <v>-76.92093</v>
-      </c>
-      <c r="I4" t="n">
-        <v>300</v>
-      </c>
-      <c r="J4" t="n">
-        <v>13</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>-12.2322</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-76.92093</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -657,20 +675,30 @@
           <t>652 03 SAN MARTIN DE PORRES</t>
         </is>
       </c>
-      <c r="G5" t="n">
-        <v>-12.23834</v>
-      </c>
-      <c r="H5" t="n">
-        <v>-76.91759</v>
-      </c>
-      <c r="I5" t="n">
-        <v>235</v>
-      </c>
-      <c r="J5" t="n">
-        <v>10</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>-12.23834</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>-76.91759</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>235</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -704,20 +732,30 @@
           <t>652 11 PEQUEÑOS QUERUBINES</t>
         </is>
       </c>
-      <c r="G6" t="n">
-        <v>-12.21539</v>
-      </c>
-      <c r="H6" t="n">
-        <v>-76.94935</v>
-      </c>
-      <c r="I6" t="n">
-        <v>227</v>
-      </c>
-      <c r="J6" t="n">
-        <v>10</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>-12.21539</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-76.94935</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>227</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -751,20 +789,30 @@
           <t>652 10</t>
         </is>
       </c>
-      <c r="G7" t="n">
-        <v>-12.1913</v>
-      </c>
-      <c r="H7" t="n">
-        <v>-76.94121</v>
-      </c>
-      <c r="I7" t="n">
-        <v>272</v>
-      </c>
-      <c r="J7" t="n">
-        <v>17</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>-12.1913</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>-76.94121</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>272</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -798,20 +846,30 @@
           <t>652-17 CAPULLITO</t>
         </is>
       </c>
-      <c r="G8" t="n">
-        <v>-12.22614</v>
-      </c>
-      <c r="H8" t="n">
-        <v>-76.9205</v>
-      </c>
-      <c r="I8" t="n">
-        <v>390</v>
-      </c>
-      <c r="J8" t="n">
-        <v>17</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>-12.22614</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>-76.9205</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>390</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -845,20 +903,30 @@
           <t>6064 FRANCISCO BOLOGNESI</t>
         </is>
       </c>
-      <c r="G9" t="n">
-        <v>-12.21011</v>
-      </c>
-      <c r="H9" t="n">
-        <v>-76.93622000000001</v>
-      </c>
-      <c r="I9" t="n">
-        <v>1473</v>
-      </c>
-      <c r="J9" t="n">
-        <v>75</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>-12.21011</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>-76.93622</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1473</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="10">
@@ -892,20 +960,30 @@
           <t>6065 PERU INGLATERRA</t>
         </is>
       </c>
-      <c r="G10" t="n">
-        <v>-12.2076</v>
-      </c>
-      <c r="H10" t="n">
-        <v>-76.9419</v>
-      </c>
-      <c r="I10" t="n">
-        <v>1604</v>
-      </c>
-      <c r="J10" t="n">
-        <v>72</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>-12.2076</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>-76.9419</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1604</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -939,20 +1017,30 @@
           <t>6066 VILLA EL SALVADOR</t>
         </is>
       </c>
-      <c r="G11" t="n">
-        <v>-12.21334</v>
-      </c>
-      <c r="H11" t="n">
-        <v>-76.93987</v>
-      </c>
-      <c r="I11" t="n">
-        <v>2593</v>
-      </c>
-      <c r="J11" t="n">
-        <v>130</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>-12.21334</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>-76.93987</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2593</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="12">
@@ -986,20 +1074,30 @@
           <t>6067 JUAN VELASCO ALVARADO</t>
         </is>
       </c>
-      <c r="G12" t="n">
-        <v>-12.2244361218332</v>
-      </c>
-      <c r="H12" t="n">
-        <v>-76.9282762820025</v>
-      </c>
-      <c r="I12" t="n">
-        <v>1021</v>
-      </c>
-      <c r="J12" t="n">
-        <v>56</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>-12.2244361218332</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>-76.9282762820025</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1021</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="13">
@@ -1033,20 +1131,30 @@
           <t>6068 MANUEL GONZALES PRADA</t>
         </is>
       </c>
-      <c r="G13" t="n">
-        <v>-12.22581</v>
-      </c>
-      <c r="H13" t="n">
-        <v>-76.93209</v>
-      </c>
-      <c r="I13" t="n">
-        <v>2026</v>
-      </c>
-      <c r="J13" t="n">
-        <v>81</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>-12.22581</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>-76.93209</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="14">
@@ -1080,20 +1188,30 @@
           <t>6071 REPUBLICA FEDERAL DE ALEMANIA</t>
         </is>
       </c>
-      <c r="G14" t="n">
-        <v>-12.2239</v>
-      </c>
-      <c r="H14" t="n">
-        <v>-76.94643000000001</v>
-      </c>
-      <c r="I14" t="n">
-        <v>2337</v>
-      </c>
-      <c r="J14" t="n">
-        <v>97</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>-12.2239</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>-76.94643</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2337</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="15">
@@ -1127,20 +1245,30 @@
           <t>6099 MI MUNDO DE COLORES / 6099 PERU ESPAÑA</t>
         </is>
       </c>
-      <c r="G15" t="n">
-        <v>-12.21089</v>
-      </c>
-      <c r="H15" t="n">
-        <v>-76.95359999999999</v>
-      </c>
-      <c r="I15" t="n">
-        <v>1357</v>
-      </c>
-      <c r="J15" t="n">
-        <v>61</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>-12.21089</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>-76.9536</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1357</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="16">
@@ -1174,20 +1302,30 @@
           <t>7090 FORJADORES DEL PERU</t>
         </is>
       </c>
-      <c r="G16" t="n">
-        <v>-12.19227</v>
-      </c>
-      <c r="H16" t="n">
-        <v>-76.94150999999999</v>
-      </c>
-      <c r="I16" t="n">
-        <v>388</v>
-      </c>
-      <c r="J16" t="n">
-        <v>14</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>-12.19227</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>-76.94151</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>388</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="17">
@@ -1221,20 +1359,30 @@
           <t>7095 PERU ITALIA</t>
         </is>
       </c>
-      <c r="G17" t="n">
-        <v>-12.19393</v>
-      </c>
-      <c r="H17" t="n">
-        <v>-76.95851</v>
-      </c>
-      <c r="I17" t="n">
-        <v>625</v>
-      </c>
-      <c r="J17" t="n">
-        <v>26</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>-12.19393</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>-76.95851</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>625</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="18">
@@ -1268,20 +1416,30 @@
           <t>7097 VILLA AMSTELVEEN</t>
         </is>
       </c>
-      <c r="G18" t="n">
-        <v>-12.21664</v>
-      </c>
-      <c r="H18" t="n">
-        <v>-76.93277999999999</v>
-      </c>
-      <c r="I18" t="n">
-        <v>782</v>
-      </c>
-      <c r="J18" t="n">
-        <v>33</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>-12.21664</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>-76.93278</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>782</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="19">
@@ -1315,20 +1473,30 @@
           <t>7215 NACIONES UNIDAS</t>
         </is>
       </c>
-      <c r="G19" t="n">
-        <v>-12.2369</v>
-      </c>
-      <c r="H19" t="n">
-        <v>-76.92089</v>
-      </c>
-      <c r="I19" t="n">
-        <v>646</v>
-      </c>
-      <c r="J19" t="n">
-        <v>27</v>
-      </c>
-      <c r="K19" t="n">
-        <v>1</v>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>-12.2369</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>-76.92089</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>646</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
     </row>
     <row r="20">
@@ -1362,20 +1530,30 @@
           <t>7216</t>
         </is>
       </c>
-      <c r="G20" t="n">
-        <v>-12.19661</v>
-      </c>
-      <c r="H20" t="n">
-        <v>-76.96223000000001</v>
-      </c>
-      <c r="I20" t="n">
-        <v>603</v>
-      </c>
-      <c r="J20" t="n">
-        <v>24</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>-12.19661</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>-76.96223</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>603</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="21">
@@ -1409,20 +1587,30 @@
           <t>REPUBLICA DE BOLIVIA</t>
         </is>
       </c>
-      <c r="G21" t="n">
-        <v>-12.19653</v>
-      </c>
-      <c r="H21" t="n">
-        <v>-76.94983000000001</v>
-      </c>
-      <c r="I21" t="n">
-        <v>1990</v>
-      </c>
-      <c r="J21" t="n">
-        <v>96</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>-12.19653</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>-76.94983</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1990</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="22">
@@ -1456,20 +1644,30 @@
           <t>7224 ELIAS REMIGIO AGUIRRE ROMERO</t>
         </is>
       </c>
-      <c r="G22" t="n">
-        <v>-12.23982</v>
-      </c>
-      <c r="H22" t="n">
-        <v>-76.91742000000001</v>
-      </c>
-      <c r="I22" t="n">
-        <v>938</v>
-      </c>
-      <c r="J22" t="n">
-        <v>53</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>-12.23982</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>-76.91742</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>938</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="23">
@@ -1503,20 +1701,30 @@
           <t>7236 MAX UHLE</t>
         </is>
       </c>
-      <c r="G23" t="n">
-        <v>-12.24546</v>
-      </c>
-      <c r="H23" t="n">
-        <v>-76.91862</v>
-      </c>
-      <c r="I23" t="n">
-        <v>846</v>
-      </c>
-      <c r="J23" t="n">
-        <v>54</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>-12.24546</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>-76.91862</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>846</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="24">
@@ -1550,20 +1758,30 @@
           <t>MANUEL GONZALES PRADA - CENTRO DE APLICACION</t>
         </is>
       </c>
-      <c r="G24" t="n">
-        <v>-12.21623</v>
-      </c>
-      <c r="H24" t="n">
-        <v>-76.93049999999999</v>
-      </c>
-      <c r="I24" t="n">
-        <v>480</v>
-      </c>
-      <c r="J24" t="n">
-        <v>18</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>-12.21623</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>-76.9305</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>480</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="25">
@@ -1597,20 +1815,30 @@
           <t>7238 SOLIDARIDAD PERU ALEMANIA</t>
         </is>
       </c>
-      <c r="G25" t="n">
-        <v>-12.23802</v>
-      </c>
-      <c r="H25" t="n">
-        <v>-76.93899</v>
-      </c>
-      <c r="I25" t="n">
-        <v>915</v>
-      </c>
-      <c r="J25" t="n">
-        <v>43</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0</v>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>-12.23802</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>-76.93899</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>915</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="26">
@@ -1644,20 +1872,30 @@
           <t>7240 JESUS DE NAZARETH</t>
         </is>
       </c>
-      <c r="G26" t="n">
-        <v>-12.24413</v>
-      </c>
-      <c r="H26" t="n">
-        <v>-76.92919000000001</v>
-      </c>
-      <c r="I26" t="n">
-        <v>1139</v>
-      </c>
-      <c r="J26" t="n">
-        <v>47</v>
-      </c>
-      <c r="K26" t="n">
-        <v>0</v>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>-12.24413</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>-76.92919</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1139</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="27">
@@ -1691,20 +1929,30 @@
           <t>BENJAMIN FRANKLIN</t>
         </is>
       </c>
-      <c r="G27" t="n">
-        <v>-12.22252</v>
-      </c>
-      <c r="H27" t="n">
-        <v>-76.92628999999999</v>
-      </c>
-      <c r="I27" t="n">
-        <v>198</v>
-      </c>
-      <c r="J27" t="n">
-        <v>18</v>
-      </c>
-      <c r="K27" t="n">
-        <v>0</v>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>-12.22252</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>-76.92629</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>198</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="28">
@@ -1738,20 +1986,30 @@
           <t>CRISTO REY DE VILLA</t>
         </is>
       </c>
-      <c r="G28" t="n">
-        <v>-12.20437</v>
-      </c>
-      <c r="H28" t="n">
-        <v>-76.93648</v>
-      </c>
-      <c r="I28" t="n">
-        <v>334</v>
-      </c>
-      <c r="J28" t="n">
-        <v>30</v>
-      </c>
-      <c r="K28" t="n">
-        <v>0</v>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>-12.20437</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>-76.93648</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>334</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="29">
@@ -1785,20 +2043,30 @@
           <t>EMMANUEL</t>
         </is>
       </c>
-      <c r="G29" t="n">
-        <v>-12.22194</v>
-      </c>
-      <c r="H29" t="n">
-        <v>-76.92251</v>
-      </c>
-      <c r="I29" t="n">
-        <v>392</v>
-      </c>
-      <c r="J29" t="n">
-        <v>18</v>
-      </c>
-      <c r="K29" t="n">
-        <v>0</v>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>-12.22194</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>-76.92251</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>392</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="30">
@@ -1832,20 +2100,30 @@
           <t>JUAN XXIII</t>
         </is>
       </c>
-      <c r="G30" t="n">
-        <v>-12.19282</v>
-      </c>
-      <c r="H30" t="n">
-        <v>-76.95905</v>
-      </c>
-      <c r="I30" t="n">
-        <v>226</v>
-      </c>
-      <c r="J30" t="n">
-        <v>19</v>
-      </c>
-      <c r="K30" t="n">
-        <v>0</v>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>-12.19282</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>-76.95905</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>226</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="31">
@@ -1879,20 +2157,30 @@
           <t>MARIA INMACULADA CONCEPCION</t>
         </is>
       </c>
-      <c r="G31" t="n">
-        <v>-12.23934</v>
-      </c>
-      <c r="H31" t="n">
-        <v>-76.92321</v>
-      </c>
-      <c r="I31" t="n">
-        <v>338</v>
-      </c>
-      <c r="J31" t="n">
-        <v>22</v>
-      </c>
-      <c r="K31" t="n">
-        <v>0</v>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>-12.23934</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>-76.92321</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>338</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="32">
@@ -1926,20 +2214,30 @@
           <t>HIPOLITO UNANUE</t>
         </is>
       </c>
-      <c r="G32" t="n">
-        <v>-12.21541</v>
-      </c>
-      <c r="H32" t="n">
-        <v>-76.94492</v>
-      </c>
-      <c r="I32" t="n">
-        <v>379</v>
-      </c>
-      <c r="J32" t="n">
-        <v>34</v>
-      </c>
-      <c r="K32" t="n">
-        <v>0</v>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>-12.21541</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>-76.94492</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>379</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="33">
@@ -1973,20 +2271,30 @@
           <t>JUAN ESPINOZA MEDRANO</t>
         </is>
       </c>
-      <c r="G33" t="n">
-        <v>-12.20411</v>
-      </c>
-      <c r="H33" t="n">
-        <v>-76.94568</v>
-      </c>
-      <c r="I33" t="n">
-        <v>365</v>
-      </c>
-      <c r="J33" t="n">
-        <v>20</v>
-      </c>
-      <c r="K33" t="n">
-        <v>0</v>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>-12.20411</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>-76.94568</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>365</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="34">
@@ -2020,20 +2328,30 @@
           <t>ALMIRANTE GUILLERMO BROWN</t>
         </is>
       </c>
-      <c r="G34" t="n">
-        <v>-12.20521</v>
-      </c>
-      <c r="H34" t="n">
-        <v>-76.93652</v>
-      </c>
-      <c r="I34" t="n">
-        <v>226</v>
-      </c>
-      <c r="J34" t="n">
-        <v>20</v>
-      </c>
-      <c r="K34" t="n">
-        <v>0</v>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>-12.20521</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>-76.93652</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>226</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="35">
@@ -2059,28 +2377,38 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>346030</t>
+          <t>346068</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>MI JESUS</t>
-        </is>
-      </c>
-      <c r="G35" t="n">
-        <v>-12.23153</v>
-      </c>
-      <c r="H35" t="n">
-        <v>-76.94123999999999</v>
-      </c>
-      <c r="I35" t="n">
-        <v>240</v>
-      </c>
-      <c r="J35" t="n">
-        <v>18</v>
-      </c>
-      <c r="K35" t="n">
-        <v>0</v>
+          <t>LA MERCED</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>-12.21278</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>-76.92647</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>746</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="36">
@@ -2106,28 +2434,38 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>346068</t>
+          <t>346209</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>LA MERCED</t>
-        </is>
-      </c>
-      <c r="G36" t="n">
-        <v>-12.21278</v>
-      </c>
-      <c r="H36" t="n">
-        <v>-76.92646999999999</v>
-      </c>
-      <c r="I36" t="n">
-        <v>746</v>
-      </c>
-      <c r="J36" t="n">
-        <v>29</v>
-      </c>
-      <c r="K36" t="n">
-        <v>0</v>
+          <t>LA MERCED KID</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>-12.21267</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>-76.92818</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>214</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="37">
@@ -2153,28 +2491,38 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>346209</t>
+          <t>522778</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>LA MERCED KID</t>
-        </is>
-      </c>
-      <c r="G37" t="n">
-        <v>-12.21267</v>
-      </c>
-      <c r="H37" t="n">
-        <v>-76.92818</v>
-      </c>
-      <c r="I37" t="n">
-        <v>214</v>
-      </c>
-      <c r="J37" t="n">
-        <v>17</v>
-      </c>
-      <c r="K37" t="n">
-        <v>0</v>
+          <t>CASA ABIERTA DE NAZARETH</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>-12.23836</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>-76.91908</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>688</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="38">
@@ -2200,28 +2548,38 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>522778</t>
+          <t>559470</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>CASA ABIERTA DE NAZARETH</t>
-        </is>
-      </c>
-      <c r="G38" t="n">
-        <v>-12.23836</v>
-      </c>
-      <c r="H38" t="n">
-        <v>-76.91907999999999</v>
-      </c>
-      <c r="I38" t="n">
-        <v>688</v>
-      </c>
-      <c r="J38" t="n">
-        <v>32</v>
-      </c>
-      <c r="K38" t="n">
-        <v>0</v>
+          <t>LUDWING VON MISSES</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>-12.19363</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>-76.94545</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>178</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="39">
@@ -2247,28 +2605,38 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>559470</t>
+          <t>687383</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>LUDWING VON MISSES</t>
-        </is>
-      </c>
-      <c r="G39" t="n">
-        <v>-12.19363</v>
-      </c>
-      <c r="H39" t="n">
-        <v>-76.94544999999999</v>
-      </c>
-      <c r="I39" t="n">
-        <v>178</v>
-      </c>
-      <c r="J39" t="n">
-        <v>23</v>
-      </c>
-      <c r="K39" t="n">
-        <v>0</v>
+          <t>7242 DIVINO MAESTRO</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>-12.21428</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>-76.92733</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>933</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="40">
@@ -2294,28 +2662,38 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>687383</t>
+          <t>688919</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>7242 DIVINO MAESTRO</t>
-        </is>
-      </c>
-      <c r="G40" t="n">
-        <v>-12.21428</v>
-      </c>
-      <c r="H40" t="n">
-        <v>-76.92733</v>
-      </c>
-      <c r="I40" t="n">
-        <v>933</v>
-      </c>
-      <c r="J40" t="n">
-        <v>40</v>
-      </c>
-      <c r="K40" t="n">
-        <v>0</v>
+          <t>SAN LORENZO</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>-12.22225</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>-76.9267</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>235</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="41">
@@ -2341,28 +2719,38 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>688919</t>
+          <t>804075</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>SAN LORENZO</t>
-        </is>
-      </c>
-      <c r="G41" t="n">
-        <v>-12.22225</v>
-      </c>
-      <c r="H41" t="n">
-        <v>-76.9267</v>
-      </c>
-      <c r="I41" t="n">
-        <v>235</v>
-      </c>
-      <c r="J41" t="n">
-        <v>23</v>
-      </c>
-      <c r="K41" t="n">
-        <v>0</v>
+          <t>651</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>-12.21774</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>-76.93546</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>246</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="42">
@@ -2388,28 +2776,38 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>804075</t>
+          <t>828972</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>651</t>
-        </is>
-      </c>
-      <c r="G42" t="n">
-        <v>-12.21774</v>
-      </c>
-      <c r="H42" t="n">
-        <v>-76.93546000000001</v>
-      </c>
-      <c r="I42" t="n">
-        <v>246</v>
-      </c>
-      <c r="J42" t="n">
-        <v>11</v>
-      </c>
-      <c r="K42" t="n">
-        <v>0</v>
+          <t>AVANTGARD COLLEGE</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>-12.2193</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>-76.95842</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1221</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="43">
@@ -2435,28 +2833,38 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>828972</t>
+          <t>837127</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>AVANTGARD COLLEGE</t>
-        </is>
-      </c>
-      <c r="G43" t="n">
-        <v>-12.2193</v>
-      </c>
-      <c r="H43" t="n">
-        <v>-76.95842</v>
-      </c>
-      <c r="I43" t="n">
-        <v>1221</v>
-      </c>
-      <c r="J43" t="n">
-        <v>59</v>
-      </c>
-      <c r="K43" t="n">
-        <v>0</v>
+          <t>URIBE'S SCHOOL</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>-12.2039</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>-76.94676</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="44">
@@ -2482,28 +2890,38 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>837127</t>
+          <t>854310</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>URIBE'S SCHOOL</t>
-        </is>
-      </c>
-      <c r="G44" t="n">
-        <v>-12.2039</v>
-      </c>
-      <c r="H44" t="n">
-        <v>-76.94676</v>
-      </c>
-      <c r="I44" t="n">
-        <v>150</v>
-      </c>
-      <c r="J44" t="n">
-        <v>5</v>
-      </c>
-      <c r="K44" t="n">
-        <v>0</v>
+          <t>INNOVA SCHOOLS - VES VALLEJO</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>-12.22237</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>-76.9567</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>766</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="45">
@@ -2529,75 +2947,38 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>854310</t>
+          <t>805942</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>INNOVA SCHOOLS - VES VALLEJO</t>
-        </is>
-      </c>
-      <c r="G45" t="n">
-        <v>-12.22237</v>
-      </c>
-      <c r="H45" t="n">
-        <v>-76.9567</v>
-      </c>
-      <c r="I45" t="n">
-        <v>766</v>
-      </c>
-      <c r="J45" t="n">
-        <v>49</v>
-      </c>
-      <c r="K45" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>150142</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>VILLA EL SALVADOR</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>805942</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
           <t>SANTISIMA VIRGEN DE LAS NIEVES</t>
         </is>
       </c>
-      <c r="G46" t="n">
-        <v>-12.19446</v>
-      </c>
-      <c r="H46" t="n">
-        <v>-76.94494</v>
-      </c>
-      <c r="I46" t="n">
-        <v>0</v>
-      </c>
-      <c r="J46" t="n">
-        <v>0</v>
-      </c>
-      <c r="K46" t="n">
-        <v>0</v>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>-12.19446</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>-76.94494</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
   </sheetData>
